--- a/output/roomself_excel/4006.xlsx
+++ b/output/roomself_excel/4006.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>240296</v>
+        <v>196930</v>
       </c>
       <c r="D2" t="n">
-        <v>4816</v>
+        <v>3764</v>
       </c>
       <c r="E2" t="n">
-        <v>828</v>
+        <v>604</v>
       </c>
       <c r="F2" t="n">
         <v>399</v>
@@ -502,6 +502,28 @@
       </c>
       <c r="F3" t="n">
         <v>189</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>43366</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1816</v>
+      </c>
+      <c r="E4" t="n">
+        <v>146</v>
+      </c>
+      <c r="F4" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/4006.xlsx
+++ b/output/roomself_excel/4006.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,11 +540,60 @@
       <c r="D2" t="n">
         <v>3764</v>
       </c>
-      <c r="E2" t="n">
-        <v>604</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>399</v>
+        <v>189</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>502</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>174</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>458</v>
+      </c>
+      <c r="P2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>60</v>
+      </c>
+      <c r="S2" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +611,37 @@
       <c r="D3" t="n">
         <v>1408</v>
       </c>
-      <c r="E3" t="n">
-        <v>236</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +658,45 @@
       <c r="D4" t="n">
         <v>1816</v>
       </c>
-      <c r="E4" t="n">
-        <v>146</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>125</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>29</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/4006.xlsx
+++ b/output/roomself_excel/4006.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,26 @@
           <t>ExtWallWidth_5</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -594,6 +614,22 @@
       </c>
       <c r="S2" t="n">
         <v>28</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>158</v>
+      </c>
+      <c r="W2" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -642,6 +678,10 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -697,6 +737,22 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>96</v>
+      </c>
+      <c r="W4" t="n">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
